--- a/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>LLY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34124100</v>
+      </c>
+      <c r="E8" s="3">
         <v>28541400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28318400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24539800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22319500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>21493300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19973800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21222100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19958700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19615600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>23113100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22603400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>24286500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7082200</v>
+      </c>
+      <c r="E9" s="3">
         <v>6629800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7312800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5483300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4721200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4681700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4447700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5654900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5037200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4932500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4908100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4796500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5067900</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>27041900</v>
+      </c>
+      <c r="E10" s="3">
         <v>21911600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21005600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19056500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>17598300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16811600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15526100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15567200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14921500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14683100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18205000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17806900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>19218600</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>9313400</v>
+      </c>
+      <c r="E12" s="3">
         <v>7190800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7025900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6085700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5595000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5051200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5096200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5243900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4796400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4733600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5531300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5278100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5020800</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3867500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1153100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1596200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>791600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>757900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2250800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2444200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>412500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1069400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>668900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>177700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>281100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>789400</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>27666200</v>
+      </c>
+      <c r="E17" s="3">
         <v>21414100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>22366500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18481800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17287900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17958800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17970500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17763300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17436000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16955800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17742700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17869200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18758000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>6457900</v>
+      </c>
+      <c r="E18" s="3">
         <v>7127300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5951900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6058000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5031600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3534500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2003300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3458800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2522700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2659800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5370400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4734200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5528500</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>582600</v>
+      </c>
+      <c r="E20" s="3">
         <v>10700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>543400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1531500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>634900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>388100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>751500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>428500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>489300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>679000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>851800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>8567800</v>
+      </c>
+      <c r="E21" s="3">
         <v>8660500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8042900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8913400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6899100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5531600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4322100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5055800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4378900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4528100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7495000</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6909100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>485900</v>
+      </c>
+      <c r="E22" s="3">
         <v>331600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>339800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>359600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>242500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>450000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>185200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>161200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>148800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>160100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>177800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>186000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>6554600</v>
+      </c>
+      <c r="E23" s="3">
         <v>6806400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6155500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7229900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5265900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3680100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2304800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3374000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2790000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3000300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5889300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5408200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5349500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>1314200</v>
+      </c>
+      <c r="E24" s="3">
         <v>561600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>573800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1036200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>628000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>354200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2188800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>636400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>381600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>609800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1204500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1319600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1001800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E26" s="3">
         <v>6244800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5581700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6193700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4637900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3325900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4493600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2737600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2408400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2390500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4684800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4088600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4347700</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E27" s="3">
         <v>6244800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5581700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6193700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4637900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3325900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4493600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2737600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2408400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2390500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4684800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4088600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4347700</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,32 +1580,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>3680500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-93900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-4697700</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-582600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-543400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1531500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-634900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-388100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-751500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-428500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-489300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-679000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-851800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E33" s="3">
         <v>6244800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5581700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6193700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8318400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3232000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-204100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2737600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2408400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2390500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4684800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4088600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4347700</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E35" s="3">
         <v>6244800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5581700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6193700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8318400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3232000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-204100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2737600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2408400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2390500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4684800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4088600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4347700</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2818600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2067000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3818500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3657100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2337500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7320700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6536200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4582100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3666400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3871600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3830200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4018800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5922500</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>109100</v>
+      </c>
+      <c r="E42" s="3">
         <v>144800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>90100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>101000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>88200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1497900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1456500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>785400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>955400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1567100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1665500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>974600</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11336200</v>
+      </c>
+      <c r="E43" s="3">
         <v>8558900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8127200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>6929000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5541500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6735200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5262200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4766300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4071600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3801300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4022800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3888300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4237900</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5772800</v>
+      </c>
+      <c r="E44" s="3">
         <v>4309700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3886000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3980300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3190700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7209900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4458300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3561900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3445800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5480000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5857600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2643800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2299800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5690300</v>
+      </c>
+      <c r="E45" s="3">
         <v>2954100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2530600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2871500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2538900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4265800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1447500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>734600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>604400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>560000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>755800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>822300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>813400</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25727000</v>
+      </c>
+      <c r="E46" s="3">
         <v>18034500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18452400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>17462100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13709600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20549600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19202100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15101400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12573600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11928300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13104700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13038700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14248200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3052200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2901800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3212600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2966800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1962400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2005400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5678800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5207500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3646600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4568900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7624900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6313300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4029800</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12913600</v>
+      </c>
+      <c r="E48" s="3">
         <v>10144000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8985100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8681900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8405000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26460100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8826500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8252600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8053500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23993200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23622200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7760200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7760300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11846300</v>
+      </c>
+      <c r="E49" s="3">
         <v>11279600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11583900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11216500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10297400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2434600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8399300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8330600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9074700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7537900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8662200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4752700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5128100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10467200</v>
+      </c>
+      <c r="E52" s="3">
         <v>7129900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6572000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6305800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4911700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10922700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2874300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1913800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2220500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7204200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2212500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2534000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2493400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64006300</v>
+      </c>
+      <c r="E54" s="3">
         <v>49489800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>48806000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>46633100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>39286100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>43908400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>44981000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38805900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>35568900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36307600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35248700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34398900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33659800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2598800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1930600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1670600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1606700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1405300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1207100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1410700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1349300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1338200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1128100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1119300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1188300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1125200</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6904500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1501100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1538300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1499300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1106700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3706600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1937400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5377400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2025200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1522300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17789900</v>
+      </c>
+      <c r="E59" s="3">
         <v>13706500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11843800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10866200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8870600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9578800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9418600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7699900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6885300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7390700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6784700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7189300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6283400</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27293200</v>
+      </c>
+      <c r="E60" s="3">
         <v>17138200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15052700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>12481600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11775200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11888100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14535900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10986600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8229600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9741000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8916600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8389500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8930900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18320800</v>
+      </c>
+      <c r="E61" s="3">
         <v>14737500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15346400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16586600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>13817900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9196400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9940500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8367800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7972400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5332800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4200300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5519400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5464700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7528600</v>
+      </c>
+      <c r="E62" s="3">
         <v>6838700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9252100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11739700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10993900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>9172500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8836700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5371000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4776600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5845700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4491100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5716100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5728600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53234400</v>
+      </c>
+      <c r="E66" s="3">
         <v>38840000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>39826800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>40991500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>36679200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>34079700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>33388800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>24798200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>20997600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20934400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>17617300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19633700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>20118100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10312300</v>
+      </c>
+      <c r="E72" s="3">
         <v>10042600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8958500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7830200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4920400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>11395900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13894100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16046300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16011800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16482700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16992400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16088200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>14897800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10771900</v>
+      </c>
+      <c r="E76" s="3">
         <v>10649800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8979200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5641600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2606900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9828700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11592200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>14007700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14571300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>15373200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17631400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14765200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13541700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5240400</v>
+      </c>
+      <c r="E81" s="3">
         <v>6244800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5581700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6193700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8318400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3232000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-204100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2737600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2408400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2390500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4684800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4088600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4347700</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1527300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1522500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1547600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1323900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1232600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1609000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1567300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1496600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1427700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1379000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1445600</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1373600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>7084400</v>
+        <v>4240100</v>
       </c>
       <c r="E89" s="3">
+        <v>7585700</v>
+      </c>
+      <c r="F89" s="3">
         <v>7260700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6499600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4836600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5524500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5615600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4851000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2964600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4458400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5735000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5304800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7234500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3447600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1854300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1309800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1387900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1033900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1210600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1076800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1037000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1066200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1162600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1012100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-905400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1692900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3261600</v>
+        <v>-7152700</v>
       </c>
       <c r="E94" s="3">
+        <v>-3762900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2762300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2258900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8082900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1906000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3783600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3139100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>26800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3909100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2072800</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4824400</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-4069300</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3535800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3086800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2687100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2409800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2311800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2192100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2158500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2127300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2101200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2120700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2187400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2180100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3495600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5406700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4131300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3137100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2324500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5904900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>142600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-559800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3111000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-166400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3829300</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2369900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-167600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-205700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>216000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-89900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-63600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-20500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-236400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-85600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-341500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21500</v>
       </c>
-      <c r="N101" s="3" t="s">
+      <c r="O101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-110900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>751600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1751500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>161400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1319600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5660700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1462000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1954100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>915700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-205200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>41400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-188600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1903700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-70700</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>LLY</t>
   </si>
@@ -777,7 +777,7 @@
         <v>6629800</v>
       </c>
       <c r="F9" s="3">
-        <v>7312800</v>
+        <v>6973100</v>
       </c>
       <c r="G9" s="3">
         <v>5483300</v>
@@ -822,7 +822,7 @@
         <v>21911600</v>
       </c>
       <c r="F10" s="3">
-        <v>21005600</v>
+        <v>21345300</v>
       </c>
       <c r="G10" s="3">
         <v>19056500</v>
@@ -886,10 +886,10 @@
         <v>7190800</v>
       </c>
       <c r="F12" s="3">
-        <v>7025900</v>
+        <v>6930700</v>
       </c>
       <c r="G12" s="3">
-        <v>6085700</v>
+        <v>5976300</v>
       </c>
       <c r="H12" s="3">
         <v>5595000</v>
@@ -970,25 +970,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>3867500</v>
+        <v>3887700</v>
       </c>
       <c r="E14" s="3">
-        <v>1153100</v>
+        <v>1563800</v>
       </c>
       <c r="F14" s="3">
-        <v>1596200</v>
+        <v>1854200</v>
       </c>
       <c r="G14" s="3">
-        <v>791600</v>
+        <v>-541200</v>
       </c>
       <c r="H14" s="3">
-        <v>757900</v>
+        <v>356700</v>
       </c>
       <c r="I14" s="3">
         <v>2250800</v>
       </c>
       <c r="J14" s="3">
-        <v>2444200</v>
+        <v>2274000</v>
       </c>
       <c r="K14" s="3">
         <v>412500</v>
@@ -1015,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1527300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1522500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1547600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1323900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1232600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1609000</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1567300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27666200</v>
+        <v>23336800</v>
       </c>
       <c r="E17" s="3">
-        <v>21414100</v>
+        <v>19888100</v>
       </c>
       <c r="F17" s="3">
-        <v>22366500</v>
+        <v>20045700</v>
       </c>
       <c r="G17" s="3">
-        <v>18481800</v>
+        <v>17329000</v>
       </c>
       <c r="H17" s="3">
-        <v>17287900</v>
+        <v>16320100</v>
       </c>
       <c r="I17" s="3">
-        <v>17958800</v>
+        <v>15467500</v>
       </c>
       <c r="J17" s="3">
-        <v>17970500</v>
+        <v>15277300</v>
       </c>
       <c r="K17" s="3">
         <v>17763300</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>6457900</v>
+        <v>10787300</v>
       </c>
       <c r="E18" s="3">
-        <v>7127300</v>
+        <v>8653300</v>
       </c>
       <c r="F18" s="3">
-        <v>5951900</v>
+        <v>8272700</v>
       </c>
       <c r="G18" s="3">
-        <v>6058000</v>
+        <v>7210800</v>
       </c>
       <c r="H18" s="3">
-        <v>5031600</v>
+        <v>5999400</v>
       </c>
       <c r="I18" s="3">
-        <v>3534500</v>
+        <v>6025800</v>
       </c>
       <c r="J18" s="3">
-        <v>2003300</v>
+        <v>4696500</v>
       </c>
       <c r="K18" s="3">
         <v>3458800</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>582600</v>
+        <v>32700</v>
       </c>
       <c r="E20" s="3">
-        <v>10700</v>
+        <v>14300</v>
       </c>
       <c r="F20" s="3">
-        <v>543400</v>
+        <v>-51400</v>
       </c>
       <c r="G20" s="3">
-        <v>1531500</v>
+        <v>195500</v>
       </c>
       <c r="H20" s="3">
-        <v>634900</v>
+        <v>56600</v>
       </c>
       <c r="I20" s="3">
-        <v>388100</v>
+        <v>11700</v>
       </c>
       <c r="J20" s="3">
-        <v>751500</v>
+        <v>59100</v>
       </c>
       <c r="K20" s="3">
         <v>100400</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>8567800</v>
+        <v>12281900</v>
       </c>
       <c r="E21" s="3">
-        <v>8660500</v>
+        <v>10161500</v>
       </c>
       <c r="F21" s="3">
-        <v>8042900</v>
+        <v>9871700</v>
       </c>
       <c r="G21" s="3">
-        <v>8913400</v>
+        <v>8339200</v>
       </c>
       <c r="H21" s="3">
-        <v>6899100</v>
+        <v>7175400</v>
       </c>
       <c r="I21" s="3">
-        <v>5531600</v>
+        <v>7623100</v>
       </c>
       <c r="J21" s="3">
-        <v>4322100</v>
+        <v>6204700</v>
       </c>
       <c r="K21" s="3">
         <v>5055800</v>
@@ -1293,7 +1293,7 @@
         <v>242500</v>
       </c>
       <c r="J22" s="3">
-        <v>450000</v>
+        <v>225000</v>
       </c>
       <c r="K22" s="3">
         <v>185200</v>
@@ -1380,10 +1380,10 @@
         <v>628000</v>
       </c>
       <c r="I24" s="3">
-        <v>354200</v>
+        <v>529500</v>
       </c>
       <c r="J24" s="3">
-        <v>-2188800</v>
+        <v>2391200</v>
       </c>
       <c r="K24" s="3">
         <v>636400</v>
@@ -1470,10 +1470,10 @@
         <v>4637900</v>
       </c>
       <c r="I26" s="3">
-        <v>3325900</v>
+        <v>3150600</v>
       </c>
       <c r="J26" s="3">
-        <v>4493600</v>
+        <v>-86400</v>
       </c>
       <c r="K26" s="3">
         <v>2737600</v>
@@ -1512,13 +1512,13 @@
         <v>6193700</v>
       </c>
       <c r="H27" s="3">
-        <v>4637900</v>
+        <v>8318400</v>
       </c>
       <c r="I27" s="3">
-        <v>3325900</v>
+        <v>3232000</v>
       </c>
       <c r="J27" s="3">
-        <v>4493600</v>
+        <v>-204100</v>
       </c>
       <c r="K27" s="3">
         <v>2737600</v>
@@ -1589,11 +1589,11 @@
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>24</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>3680500</v>
       </c>
       <c r="I29" s="3">
-        <v>-93900</v>
+        <v>81400</v>
       </c>
       <c r="J29" s="3">
-        <v>-4697700</v>
+        <v>-117700</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>24</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-582600</v>
+        <v>-32700</v>
       </c>
       <c r="E32" s="3">
-        <v>-10700</v>
+        <v>-14300</v>
       </c>
       <c r="F32" s="3">
-        <v>-543400</v>
+        <v>51400</v>
       </c>
       <c r="G32" s="3">
-        <v>-1531500</v>
+        <v>-195500</v>
       </c>
       <c r="H32" s="3">
-        <v>-634900</v>
+        <v>-56600</v>
       </c>
       <c r="I32" s="3">
-        <v>-388100</v>
+        <v>-11700</v>
       </c>
       <c r="J32" s="3">
-        <v>-751500</v>
+        <v>-59100</v>
       </c>
       <c r="K32" s="3">
         <v>-100400</v>
@@ -2038,13 +2038,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>109100</v>
+        <v>222900</v>
       </c>
       <c r="E42" s="3">
-        <v>144800</v>
+        <v>375300</v>
       </c>
       <c r="F42" s="3">
-        <v>90100</v>
+        <v>94900</v>
       </c>
       <c r="G42" s="3">
         <v>24200</v>
@@ -2053,10 +2053,10 @@
         <v>101000</v>
       </c>
       <c r="I42" s="3">
-        <v>88200</v>
+        <v>157400</v>
       </c>
       <c r="J42" s="3">
-        <v>1497900</v>
+        <v>1498700</v>
       </c>
       <c r="K42" s="3">
         <v>1456500</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11336200</v>
+        <v>11092800</v>
       </c>
       <c r="E43" s="3">
-        <v>8558900</v>
+        <v>8301800</v>
       </c>
       <c r="F43" s="3">
-        <v>8127200</v>
+        <v>8112500</v>
       </c>
       <c r="G43" s="3">
-        <v>6929000</v>
+        <v>6887900</v>
       </c>
       <c r="H43" s="3">
-        <v>5541500</v>
+        <v>5523100</v>
       </c>
       <c r="I43" s="3">
-        <v>6735200</v>
+        <v>5696300</v>
       </c>
       <c r="J43" s="3">
-        <v>5262200</v>
+        <v>5234600</v>
       </c>
       <c r="K43" s="3">
         <v>4766300</v>
@@ -2143,7 +2143,7 @@
         <v>3190700</v>
       </c>
       <c r="I44" s="3">
-        <v>7209900</v>
+        <v>3098100</v>
       </c>
       <c r="J44" s="3">
         <v>4458300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5690300</v>
+        <v>279100</v>
       </c>
       <c r="E45" s="3">
-        <v>2954100</v>
+        <v>33900</v>
       </c>
       <c r="F45" s="3">
-        <v>2530600</v>
+        <v>9900</v>
       </c>
       <c r="G45" s="3">
-        <v>2871500</v>
+        <v>41100</v>
       </c>
       <c r="H45" s="3">
-        <v>2538900</v>
+        <v>18400</v>
       </c>
       <c r="I45" s="3">
-        <v>4265800</v>
+        <v>2240400</v>
       </c>
       <c r="J45" s="3">
-        <v>1447500</v>
+        <v>26800</v>
       </c>
       <c r="K45" s="3">
         <v>734600</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3052200</v>
+        <v>3406500</v>
       </c>
       <c r="E47" s="3">
-        <v>2901800</v>
+        <v>3200900</v>
       </c>
       <c r="F47" s="3">
-        <v>3212600</v>
+        <v>3404600</v>
       </c>
       <c r="G47" s="3">
-        <v>2966800</v>
+        <v>3198200</v>
       </c>
       <c r="H47" s="3">
-        <v>1962400</v>
+        <v>2125800</v>
       </c>
       <c r="I47" s="3">
-        <v>2005400</v>
+        <v>2018100</v>
       </c>
       <c r="J47" s="3">
-        <v>5678800</v>
+        <v>5713900</v>
       </c>
       <c r="K47" s="3">
         <v>5207500</v>
@@ -2320,10 +2320,10 @@
         <v>8681900</v>
       </c>
       <c r="H48" s="3">
-        <v>8405000</v>
+        <v>7872900</v>
       </c>
       <c r="I48" s="3">
-        <v>26460100</v>
+        <v>7996100</v>
       </c>
       <c r="J48" s="3">
         <v>8826500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10467200</v>
+        <v>4635600</v>
       </c>
       <c r="E52" s="3">
-        <v>7129900</v>
+        <v>4037900</v>
       </c>
       <c r="F52" s="3">
-        <v>6572000</v>
+        <v>3890700</v>
       </c>
       <c r="G52" s="3">
-        <v>6305800</v>
+        <v>3244000</v>
       </c>
       <c r="H52" s="3">
-        <v>4911700</v>
+        <v>2707800</v>
       </c>
       <c r="I52" s="3">
-        <v>10922700</v>
+        <v>8296300</v>
       </c>
       <c r="J52" s="3">
-        <v>2874300</v>
+        <v>1672800</v>
       </c>
       <c r="K52" s="3">
         <v>1913800</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6904500</v>
+        <v>7132300</v>
       </c>
       <c r="E58" s="3">
         <v>1501100</v>
       </c>
       <c r="F58" s="3">
-        <v>1538300</v>
+        <v>1539500</v>
       </c>
       <c r="G58" s="3">
-        <v>8700</v>
+        <v>101300</v>
       </c>
       <c r="H58" s="3">
-        <v>1499300</v>
+        <v>1520700</v>
       </c>
       <c r="I58" s="3">
-        <v>1106700</v>
+        <v>1133700</v>
       </c>
       <c r="J58" s="3">
-        <v>3706600</v>
+        <v>3740200</v>
       </c>
       <c r="K58" s="3">
         <v>1937400</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>17789900</v>
+        <v>4144000</v>
       </c>
       <c r="E59" s="3">
-        <v>13706500</v>
+        <v>3783800</v>
       </c>
       <c r="F59" s="3">
-        <v>11843800</v>
+        <v>3962500</v>
       </c>
       <c r="G59" s="3">
-        <v>10866200</v>
+        <v>3848100</v>
       </c>
       <c r="H59" s="3">
-        <v>8870600</v>
+        <v>2927500</v>
       </c>
       <c r="I59" s="3">
-        <v>9578800</v>
+        <v>3670700</v>
       </c>
       <c r="J59" s="3">
-        <v>9418600</v>
+        <v>3850100</v>
       </c>
       <c r="K59" s="3">
         <v>7699900</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>18320800</v>
+        <v>19335000</v>
       </c>
       <c r="E61" s="3">
-        <v>14737500</v>
+        <v>14871800</v>
       </c>
       <c r="F61" s="3">
-        <v>15346400</v>
+        <v>15387000</v>
       </c>
       <c r="G61" s="3">
-        <v>16586600</v>
+        <v>16784500</v>
       </c>
       <c r="H61" s="3">
-        <v>13817900</v>
+        <v>13843700</v>
       </c>
       <c r="I61" s="3">
-        <v>9196400</v>
+        <v>9241200</v>
       </c>
       <c r="J61" s="3">
-        <v>9940500</v>
+        <v>9977000</v>
       </c>
       <c r="K61" s="3">
         <v>8367800</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>7528600</v>
+        <v>5075600</v>
       </c>
       <c r="E62" s="3">
-        <v>6838700</v>
+        <v>5399300</v>
       </c>
       <c r="F62" s="3">
-        <v>9252100</v>
+        <v>5523700</v>
       </c>
       <c r="G62" s="3">
-        <v>11739700</v>
+        <v>5347400</v>
       </c>
       <c r="H62" s="3">
-        <v>10993900</v>
+        <v>5082400</v>
       </c>
       <c r="I62" s="3">
-        <v>9172500</v>
+        <v>7755100</v>
       </c>
       <c r="J62" s="3">
-        <v>8836700</v>
+        <v>5286300</v>
       </c>
       <c r="K62" s="3">
         <v>5371000</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>53234400</v>
+        <v>53142600</v>
       </c>
       <c r="E66" s="3">
-        <v>38840000</v>
+        <v>38714400</v>
       </c>
       <c r="F66" s="3">
-        <v>39826800</v>
+        <v>39651200</v>
       </c>
       <c r="G66" s="3">
-        <v>40991500</v>
+        <v>40807900</v>
       </c>
       <c r="H66" s="3">
-        <v>36679200</v>
+        <v>36587000</v>
       </c>
       <c r="I66" s="3">
-        <v>34079700</v>
+        <v>32999300</v>
       </c>
       <c r="J66" s="3">
-        <v>33388800</v>
+        <v>33313100</v>
       </c>
       <c r="K66" s="3">
         <v>24798200</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1527300</v>
+        <v>1021700</v>
       </c>
       <c r="E83" s="3">
-        <v>1522500</v>
+        <v>942800</v>
       </c>
       <c r="F83" s="3">
-        <v>1547600</v>
+        <v>918800</v>
       </c>
       <c r="G83" s="3">
-        <v>1323900</v>
+        <v>895700</v>
       </c>
       <c r="H83" s="3">
-        <v>1232600</v>
+        <v>1006800</v>
       </c>
       <c r="I83" s="3">
-        <v>1609000</v>
+        <v>1247700</v>
       </c>
       <c r="J83" s="3">
-        <v>1567300</v>
+        <v>1105100</v>
       </c>
       <c r="K83" s="3">
         <v>1496600</v>
@@ -3970,7 +3970,7 @@
         <v>7585700</v>
       </c>
       <c r="F89" s="3">
-        <v>7260700</v>
+        <v>7365900</v>
       </c>
       <c r="G89" s="3">
         <v>6499600</v>
@@ -4169,7 +4169,7 @@
         <v>-3762900</v>
       </c>
       <c r="F94" s="3">
-        <v>-2762300</v>
+        <v>-2867500</v>
       </c>
       <c r="G94" s="3">
         <v>-2258900</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4069300</v>
+        <v>4069300</v>
       </c>
       <c r="E96" s="3">
-        <v>-3535800</v>
+        <v>3535800</v>
       </c>
       <c r="F96" s="3">
-        <v>-3086800</v>
+        <v>3086800</v>
       </c>
       <c r="G96" s="3">
-        <v>-2687100</v>
+        <v>2687100</v>
       </c>
       <c r="H96" s="3">
-        <v>-2409800</v>
+        <v>2409800</v>
       </c>
       <c r="I96" s="3">
-        <v>-2311800</v>
+        <v>2311800</v>
       </c>
       <c r="J96" s="3">
-        <v>-2192100</v>
+        <v>2192100</v>
       </c>
       <c r="K96" s="3">
         <v>-2158500</v>

--- a/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>45042700</v>
+      </c>
+      <c r="E8" s="3">
         <v>34124100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28541400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28318400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24539800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22319500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>21493300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19973800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21222100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19958700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19615600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23113100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22603400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>24286500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8418300</v>
+      </c>
+      <c r="E9" s="3">
         <v>7082200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>6629800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6973100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5483300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4721200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4681700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4447700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5654900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5037200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4932500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4908100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4796500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5067900</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>36624400</v>
+      </c>
+      <c r="E10" s="3">
         <v>27041900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>21911600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>21345300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>19056500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>17598300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16811600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15526100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15567200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14921500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14683100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18205000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17806900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>19218600</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,53 +886,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10990600</v>
+      </c>
+      <c r="E12" s="3">
         <v>9313400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7190800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6930700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5976300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5595000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5051200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5096200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5243900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4796400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4733600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5531300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5278100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5020800</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>4190500</v>
+      </c>
+      <c r="E14" s="3">
         <v>3887700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1563800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1854200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-541200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>356700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2250800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2274000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>412500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1069400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>668900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>177700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>281100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>789400</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1766600</v>
+      </c>
+      <c r="E15" s="3">
         <v>1527300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1522500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1547600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1323900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1232600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1609000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1567300</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>27541000</v>
+      </c>
+      <c r="E17" s="3">
         <v>23336800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19888100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20045700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17329000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16320100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15467500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15277300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17763300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17436000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16955800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17742700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17869200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18758000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>17501700</v>
+      </c>
+      <c r="E18" s="3">
         <v>10787300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8653300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8272700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7210800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5999400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6025800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4696500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3458800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2522700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2659800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5370400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4734200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5528500</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E20" s="3">
         <v>32700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-51400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>195500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>56600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>11700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>59100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>428500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>489300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>679000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>851800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>19242900</v>
+      </c>
+      <c r="E21" s="3">
         <v>12281900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10161500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9871700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8339200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7175400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7623100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6204700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5055800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>4378900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4528100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7495000</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6909100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>780600</v>
+      </c>
+      <c r="E22" s="3">
         <v>485900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>331600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>339800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>359600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>242500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>225000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>185200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>161200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>148800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>160100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>177800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>186000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>12680400</v>
+      </c>
+      <c r="E23" s="3">
         <v>6554600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6806400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6155500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7229900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5265900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3680100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2304800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3374000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2790000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3000300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5889300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5408200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5349500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>2090400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1314200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>561600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>573800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1036200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>628000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>529500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2391200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>636400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>381600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>609800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1204500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1319600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1001800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>10590000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5240400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6244800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5581700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6193700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4637900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3150600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-86400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2737600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2408400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2390500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4684800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4088600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4347700</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>10590000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5240400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6244800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5581700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6193700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8318400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3232000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-204100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2737600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2408400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2390500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4684800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4088600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4347700</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1602,16 +1662,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>3680500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>81400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-117700</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>24</v>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-32700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>51400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-195500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-56600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-11700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-59100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-428500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-489300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-679000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-851800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10590000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5240400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6244800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5581700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6193700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8318400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3232000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-204100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2737600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2408400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2390500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4684800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4088600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4347700</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10590000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5240400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6244800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5581700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6193700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8318400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3232000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-204100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2737600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2408400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2390500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4684800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4088600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4347700</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3268400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2818600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2067000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3818500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3657100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2337500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7320700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6536200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4582100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3666400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3871600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3830200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4018800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5922500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E42" s="3">
         <v>222900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>375300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>94900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>24200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>157400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1498700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1456500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>785400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>955400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1567100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1665500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>974600</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>12928600</v>
+      </c>
+      <c r="E43" s="3">
         <v>11092800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8301800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8112500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>6887900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5523100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5696300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5234600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4766300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4071600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3801300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4022800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3888300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4237900</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7589200</v>
+      </c>
+      <c r="E44" s="3">
         <v>5772800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4309700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3886000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3980300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3190700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3098100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4458300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3561900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3445800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5480000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5857600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2643800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2299800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>447900</v>
+      </c>
+      <c r="E45" s="3">
         <v>279100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>33900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2240400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>734600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>604400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>560000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>755800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>822300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>813400</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>32739700</v>
+      </c>
+      <c r="E46" s="3">
         <v>25727000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18034500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18452400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17462100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13709600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>20549600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19202100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15101400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12573600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11928300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13104700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13038700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14248200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3266600</v>
+      </c>
+      <c r="E47" s="3">
         <v>3406500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3200900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3404600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3198200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2125800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2018100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5713900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5207500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3646600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4568900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7624900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6313300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4029800</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17102400</v>
+      </c>
+      <c r="E48" s="3">
         <v>12913600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>10144000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8985100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8681900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>7872900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7996100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8826500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8252600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8053500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23993200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23622200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7760200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7760300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11936600</v>
+      </c>
+      <c r="E49" s="3">
         <v>11846300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11279600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11583900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11216500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10297400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2434600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8399300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8330600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9074700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7537900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8662200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4752700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5128100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5669000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4635600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4037900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3890700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3244000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2707800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8296300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1672800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1913800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2220500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7204200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2212500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2534000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2493400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78714900</v>
+      </c>
+      <c r="E54" s="3">
         <v>64006300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>49489800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>48806000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>46633100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>39286100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>43908400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>44981000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38805900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>35568900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36307600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35248700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34398900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>33659800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3228600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2598800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1930600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1670600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1606700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1405300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1207100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1410700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1349300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1338200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1128100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1119300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1188300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1125200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7132300</v>
+        <v>5294800</v>
       </c>
       <c r="E58" s="3">
+        <v>7091600</v>
+      </c>
+      <c r="F58" s="3">
         <v>1501100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1539500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>101300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1520700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1133700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3740200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1937400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5377400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2025200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1522300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4144000</v>
+        <v>6140400</v>
       </c>
       <c r="E59" s="3">
+        <v>4184700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3783800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3962500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3848100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2927500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3670700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3850100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7699900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6885300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7390700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6784700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7189300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6283400</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>28376600</v>
+      </c>
+      <c r="E60" s="3">
         <v>27293200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17138200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15052700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12481600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11775200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11888100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14535900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10986600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8229600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9741000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8916600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8389500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8930900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19335000</v>
+        <v>29615800</v>
       </c>
       <c r="E61" s="3">
+        <v>19373100</v>
+      </c>
+      <c r="F61" s="3">
         <v>14871800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15387000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>16784500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>13843700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9241200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9977000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8367800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7972400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5332800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4200300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5519400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5464700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5075600</v>
+        <v>5150400</v>
       </c>
       <c r="E62" s="3">
+        <v>5037500</v>
+      </c>
+      <c r="F62" s="3">
         <v>5399300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5523700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5347400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5082400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7755100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5286300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5371000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4776600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5845700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4491100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5716100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5728600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64443300</v>
+      </c>
+      <c r="E66" s="3">
         <v>53142600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>38714400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>39651200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>40807900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>36587000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32999300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>33313100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24798200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20997600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20934400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>17617300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19633700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20118100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>13545000</v>
+      </c>
+      <c r="E72" s="3">
         <v>10312300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10042600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8958500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7830200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4920400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11395900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13894100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16046300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16011800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16482700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16992400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16088200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>14897800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14192100</v>
+      </c>
+      <c r="E76" s="3">
         <v>10771900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10649800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8979200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5641600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2606900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9828700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11592200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14007700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14571300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15373200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>17631400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14765200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13541700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10590000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5240400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6244800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5581700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6193700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8318400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3232000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-204100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2737600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2408400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2390500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4684800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4088600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4347700</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1213700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1021700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>942800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>918800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>895700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1006800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1247700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1105100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1496600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1427700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1379000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1445600</v>
       </c>
-      <c r="O83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1373600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8817900</v>
+      </c>
+      <c r="E89" s="3">
         <v>4240100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7585700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7365900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6499600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4836600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5524500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5615600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4851000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2964600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4458400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5735000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5304800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7234500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5057800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3447600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1854300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1309800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1387900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1033900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1210600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1076800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1037000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1066200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1162600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1012100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-905400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1692900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9301500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7152700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3762900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2867500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2258900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8082900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1906000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3783600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3139100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>26800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3909100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2072800</v>
       </c>
-      <c r="O94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4824400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4680400</v>
+      </c>
+      <c r="E96" s="3">
         <v>4069300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3535800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3086800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2687100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2409800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2311800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2192100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2158500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2127300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2101200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2120700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2187400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2180100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1230100</v>
+      </c>
+      <c r="E100" s="3">
         <v>3495600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5406700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4131300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3137100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2324500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5904900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>142600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-559800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3111000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-166400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3829300</v>
       </c>
-      <c r="O100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2369900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-296700</v>
+      </c>
+      <c r="E101" s="3">
         <v>168600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-167600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-205700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>216000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-89900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-63600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-20500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-236400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-85600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-341500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21500</v>
       </c>
-      <c r="O101" s="3" t="s">
+      <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-110900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>449800</v>
+      </c>
+      <c r="E102" s="3">
         <v>751600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1751500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>161400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1319600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5660700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1462000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1954100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>915700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-205200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>41400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-188600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1903700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
@@ -2415,10 +2415,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17102400</v>
+        <v>18152500</v>
       </c>
       <c r="E48" s="3">
-        <v>12913600</v>
+        <v>13937800</v>
       </c>
       <c r="F48" s="3">
         <v>10144000</v>
@@ -2607,10 +2607,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5669000</v>
+        <v>4618900</v>
       </c>
       <c r="E52" s="3">
-        <v>4635600</v>
+        <v>3611400</v>
       </c>
       <c r="F52" s="3">
         <v>4037900</v>

--- a/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LLY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>LLY</t>
   </si>
@@ -656,219 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>45042700</v>
+        <v>65179000</v>
       </c>
       <c r="E8" s="3">
-        <v>34124100</v>
+        <v>45043000</v>
       </c>
       <c r="F8" s="3">
+        <v>34124000</v>
+      </c>
+      <c r="G8" s="3">
         <v>28541400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>28318400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24539800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22319500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21493300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19973800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21222100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19958700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19615600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23113100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22603400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24286500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>8418300</v>
+        <v>11052000</v>
       </c>
       <c r="E9" s="3">
-        <v>7082200</v>
+        <v>8418000</v>
       </c>
       <c r="F9" s="3">
+        <v>7082000</v>
+      </c>
+      <c r="G9" s="3">
         <v>6629800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6973100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5483300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4721200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4681700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4447700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5654900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5037200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4932500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4908100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4796500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5067900</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>36624400</v>
+        <v>54127000</v>
       </c>
       <c r="E10" s="3">
-        <v>27041900</v>
+        <v>36625000</v>
       </c>
       <c r="F10" s="3">
+        <v>27042000</v>
+      </c>
+      <c r="G10" s="3">
         <v>21911600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21345300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19056500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>17598300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16811600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15526100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15567200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14921500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>14683100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18205000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17806900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>19218600</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>10990600</v>
+        <v>13337000</v>
       </c>
       <c r="E12" s="3">
-        <v>9313400</v>
+        <v>10991000</v>
       </c>
       <c r="F12" s="3">
+        <v>9313000</v>
+      </c>
+      <c r="G12" s="3">
         <v>7190800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6930700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5976300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5595000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5051200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5096200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5243900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4796400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4733600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5531300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5278100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5020800</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,87 +999,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>4190500</v>
+        <v>3394000</v>
       </c>
       <c r="E14" s="3">
-        <v>3887700</v>
+        <v>4141000</v>
       </c>
       <c r="F14" s="3">
+        <v>3868000</v>
+      </c>
+      <c r="G14" s="3">
         <v>1563800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1854200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-541200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>356700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2250800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2274000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>412500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1069400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>668900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>177700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>281100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>789400</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>1766600</v>
+        <v>1997000</v>
       </c>
       <c r="E15" s="3">
-        <v>1527300</v>
+        <v>1767000</v>
       </c>
       <c r="F15" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1522500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1547600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1323900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1232600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1609000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1567300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>27541000</v>
+        <v>35483000</v>
       </c>
       <c r="E17" s="3">
-        <v>23336800</v>
+        <v>28003000</v>
       </c>
       <c r="F17" s="3">
+        <v>23799000</v>
+      </c>
+      <c r="G17" s="3">
         <v>19888100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>20045700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17329000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16320100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15467500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15277300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17763300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17436000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16955800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17742700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17869200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18758000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>17501700</v>
+        <v>29696000</v>
       </c>
       <c r="E18" s="3">
-        <v>10787300</v>
+        <v>17040000</v>
       </c>
       <c r="F18" s="3">
+        <v>10325000</v>
+      </c>
+      <c r="G18" s="3">
         <v>8653300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8272700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7210800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5999400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6025800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4696500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3458800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2522700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2659800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5370400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4734200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5528500</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>25400</v>
+        <v>571000</v>
       </c>
       <c r="E20" s="3">
-        <v>32700</v>
+        <v>219000</v>
       </c>
       <c r="F20" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="G20" s="3">
         <v>14300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-51400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>195500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>56600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>11700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>59100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>428500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>489300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>679000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>851800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>19242900</v>
+        <v>31122000</v>
       </c>
       <c r="E21" s="3">
-        <v>12281900</v>
+        <v>18588000</v>
       </c>
       <c r="F21" s="3">
+        <v>11949000</v>
+      </c>
+      <c r="G21" s="3">
         <v>10161500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9871700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8339200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7175400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7623100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6204700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5055800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4378900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4528100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7495000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6909100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>780600</v>
-      </c>
-      <c r="E22" s="3">
-        <v>485900</v>
-      </c>
-      <c r="F22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3">
         <v>331600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>339800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>359600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>242500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>225000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>185200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>161200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>148800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>160100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>177800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>186000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>12680400</v>
+        <v>25731000</v>
       </c>
       <c r="E23" s="3">
-        <v>6554600</v>
+        <v>12680000</v>
       </c>
       <c r="F23" s="3">
+        <v>6554000</v>
+      </c>
+      <c r="G23" s="3">
         <v>6806400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6155500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7229900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5265900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3680100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2304800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3374000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2790000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3000300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5889300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5408200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5349500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>2090400</v>
+        <v>5091000</v>
       </c>
       <c r="E24" s="3">
-        <v>1314200</v>
+        <v>2090000</v>
       </c>
       <c r="F24" s="3">
+        <v>1314000</v>
+      </c>
+      <c r="G24" s="3">
         <v>561600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>573800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1036200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>628000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>529500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2391200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>636400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>381600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>609800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1204500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1319600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1001800</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1499,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>20640000</v>
+      </c>
+      <c r="E26" s="3">
         <v>10590000</v>
       </c>
-      <c r="E26" s="3">
-        <v>5240400</v>
-      </c>
       <c r="F26" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="G26" s="3">
         <v>6244800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5581700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6193700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4637900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3150600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-86400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2737600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2408400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2390500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4684800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4088600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4347700</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>20640000</v>
+      </c>
+      <c r="E27" s="3">
         <v>10590000</v>
       </c>
-      <c r="E27" s="3">
-        <v>5240400</v>
-      </c>
       <c r="F27" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="G27" s="3">
         <v>6244800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5581700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6193700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8318400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3232000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-204100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2737600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2408400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2390500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4684800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4088600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4347700</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1643,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1665,16 +1726,16 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>3680500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>81400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-117700</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1691,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-25400</v>
+        <v>-571000</v>
       </c>
       <c r="E32" s="3">
-        <v>-32700</v>
+        <v>-219000</v>
       </c>
       <c r="F32" s="3">
+        <v>97000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-14300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>51400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-195500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-56600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-11700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-59100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-428500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-489300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-679000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-851800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>20640000</v>
+      </c>
+      <c r="E33" s="3">
         <v>10590000</v>
       </c>
-      <c r="E33" s="3">
-        <v>5240400</v>
-      </c>
       <c r="F33" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="G33" s="3">
         <v>6244800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5581700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6193700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8318400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3232000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-204100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2737600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2408400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2390500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4684800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4088600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4347700</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>20640000</v>
+      </c>
+      <c r="E35" s="3">
         <v>10590000</v>
       </c>
-      <c r="E35" s="3">
-        <v>5240400</v>
-      </c>
       <c r="F35" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="G35" s="3">
         <v>6244800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5581700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6193700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8318400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3232000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-204100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2737600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2408400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2390500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4684800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4088600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4347700</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2159,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3268400</v>
+        <v>7268000</v>
       </c>
       <c r="E41" s="3">
+        <v>3268000</v>
+      </c>
+      <c r="F41" s="3">
         <v>2818600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2067000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3818500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3657100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2337500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7320700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6536200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4582100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3666400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3871600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3830200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4018800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5922500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>165100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>222900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>375300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>94900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>24200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>101000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>157400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1498700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1456500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>785400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>955400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1567100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1665500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>974600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>12928600</v>
+        <v>20116000</v>
       </c>
       <c r="E43" s="3">
+        <v>12939000</v>
+      </c>
+      <c r="F43" s="3">
         <v>11092800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8301800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8112500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6887900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5523100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5696300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5234600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4766300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4071600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3801300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4022800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3888300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>4237900</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7589200</v>
+        <v>13744000</v>
       </c>
       <c r="E44" s="3">
+        <v>7589000</v>
+      </c>
+      <c r="F44" s="3">
         <v>5772800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4309700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3886000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3980300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3190700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3098100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4458300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3561900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3445800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5480000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5857600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2643800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2299800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>447900</v>
+        <v>13086000</v>
       </c>
       <c r="E45" s="3">
+        <v>7703000</v>
+      </c>
+      <c r="F45" s="3">
         <v>279100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2240400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>734600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>604400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>560000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>755800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>822300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>813400</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>32739700</v>
+        <v>55629000</v>
       </c>
       <c r="E46" s="3">
+        <v>32740000</v>
+      </c>
+      <c r="F46" s="3">
         <v>25727000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18034500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18452400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>17462100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13709600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20549600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19202100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15101400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12573600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11928300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13104700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13038700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14248200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3266600</v>
+        <v>2802000</v>
       </c>
       <c r="E47" s="3">
+        <v>3216000</v>
+      </c>
+      <c r="F47" s="3">
         <v>3406500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3200900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3404600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3198200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2125800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2018100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5713900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5207500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3646600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4568900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7624900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6313300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4029800</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18152500</v>
+        <v>25935000</v>
       </c>
       <c r="E48" s="3">
+        <v>18152000</v>
+      </c>
+      <c r="F48" s="3">
         <v>13937800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>10144000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8985100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8681900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>7872900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>7996100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8826500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8252600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8053500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23993200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23622200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7760200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7760300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>11936600</v>
+        <v>12419000</v>
       </c>
       <c r="E49" s="3">
+        <v>11936000</v>
+      </c>
+      <c r="F49" s="3">
         <v>11846300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11279600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11583900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11216500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10297400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2434600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8399300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8330600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9074700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7537900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8662200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4752700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5128100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4618900</v>
+        <v>5732000</v>
       </c>
       <c r="E52" s="3">
+        <v>4670000</v>
+      </c>
+      <c r="F52" s="3">
         <v>3611400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4037900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3890700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3244000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2707800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8296300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1672800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1913800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2220500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7204200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2212500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2534000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2493400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>78714900</v>
+        <v>112476000</v>
       </c>
       <c r="E54" s="3">
+        <v>78715000</v>
+      </c>
+      <c r="F54" s="3">
         <v>64006300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>49489800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>48806000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46633100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>39286100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>43908400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>44981000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38805900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>35568900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36307600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>35248700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34398900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>33659800</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3228600</v>
+        <v>5379000</v>
       </c>
       <c r="E57" s="3">
+        <v>3229000</v>
+      </c>
+      <c r="F57" s="3">
         <v>2598800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1930600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1670600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1606700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1405300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1207100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1410700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1349300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1338200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1128100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1119300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1188300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1125200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5294800</v>
+        <v>1857000</v>
       </c>
       <c r="E58" s="3">
+        <v>5293000</v>
+      </c>
+      <c r="F58" s="3">
         <v>7091600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1501100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1539500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>101300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1520700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1133700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3740200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1937400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5377400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2025200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1522300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>6140400</v>
+        <v>8235000</v>
       </c>
       <c r="E59" s="3">
+        <v>6221000</v>
+      </c>
+      <c r="F59" s="3">
         <v>4184700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3783800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3962500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3848100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2927500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3670700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3850100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7699900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6885300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7390700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6784700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7189300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6283400</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>28376600</v>
+        <v>35228000</v>
       </c>
       <c r="E60" s="3">
+        <v>28376000</v>
+      </c>
+      <c r="F60" s="3">
         <v>27293200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>17138200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15052700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12481600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11775200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11888100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14535900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10986600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8229600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9741000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8916600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8389500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8930900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>29615800</v>
+        <v>42008000</v>
       </c>
       <c r="E61" s="3">
+        <v>29498000</v>
+      </c>
+      <c r="F61" s="3">
         <v>19373100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>14871800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>15387000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>16784500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>13843700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9241200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9977000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8367800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7972400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5332800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4200300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5519400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5464700</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5150400</v>
+        <v>8705000</v>
       </c>
       <c r="E62" s="3">
+        <v>6569000</v>
+      </c>
+      <c r="F62" s="3">
         <v>5037500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5399300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5523700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5347400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5082400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7755100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5286300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5371000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4776600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5845700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4491100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5716100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5728600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3168,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>64443300</v>
+        <v>85941000</v>
       </c>
       <c r="E66" s="3">
+        <v>64443000</v>
+      </c>
+      <c r="F66" s="3">
         <v>53142600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38714400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>39651200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>40807900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>36587000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>32999300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>33313100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>24798200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20997600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20934400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17617300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19633700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>20118100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24470000</v>
+      </c>
+      <c r="E72" s="3">
         <v>13545000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10312300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10042600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8958500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7830200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4920400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11395900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13894100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16046300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>16011800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>16482700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>16992400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16088200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14897800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>14192100</v>
+        <v>26535000</v>
       </c>
       <c r="E76" s="3">
+        <v>14272000</v>
+      </c>
+      <c r="F76" s="3">
         <v>10771900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10649800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8979200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5641600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2606900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9828700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11592200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14007700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14571300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15373200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>17631400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14765200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13541700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>20640000</v>
+      </c>
+      <c r="E81" s="3">
         <v>10590000</v>
       </c>
-      <c r="E81" s="3">
-        <v>5240400</v>
-      </c>
       <c r="F81" s="3">
+        <v>5240000</v>
+      </c>
+      <c r="G81" s="3">
         <v>6244800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5581700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6193700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8318400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3232000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-204100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2737600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2408400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2390500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4684800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4088600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4347700</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1213700</v>
+        <v>1509000</v>
       </c>
       <c r="E83" s="3">
-        <v>1021700</v>
+        <v>1214000</v>
       </c>
       <c r="F83" s="3">
+        <v>1021000</v>
+      </c>
+      <c r="G83" s="3">
         <v>942800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>918800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>895700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1006800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1247700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1105100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1496600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1427700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1379000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1445600</v>
       </c>
-      <c r="P83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1373600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>8817900</v>
+        <v>16813000</v>
       </c>
       <c r="E89" s="3">
-        <v>4240100</v>
+        <v>8818000</v>
       </c>
       <c r="F89" s="3">
+        <v>4240000</v>
+      </c>
+      <c r="G89" s="3">
         <v>7585700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7365900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6499600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4836600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5524500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5615600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4851000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2964600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4458400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5735000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5304800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7234500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-5057800</v>
+        <v>-7841000</v>
       </c>
       <c r="E91" s="3">
-        <v>-3447600</v>
+        <v>-5058000</v>
       </c>
       <c r="F91" s="3">
+        <v>-3448000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1854300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1309800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1387900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1033900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1210600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1076800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1037000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1066200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1162600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1012100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-905400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1692900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-9301500</v>
+        <v>-10972000</v>
       </c>
       <c r="E94" s="3">
-        <v>-7152700</v>
+        <v>-9302000</v>
       </c>
       <c r="F94" s="3">
+        <v>-7153000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-3762900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2867500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2258900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8082900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1906000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3783600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3139100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>26800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3909100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2072800</v>
       </c>
-      <c r="P94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4824400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4687,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4680400</v>
+        <v>5384000</v>
       </c>
       <c r="E96" s="3">
-        <v>4069300</v>
+        <v>4680000</v>
       </c>
       <c r="F96" s="3">
+        <v>4069000</v>
+      </c>
+      <c r="G96" s="3">
         <v>3535800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3086800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2687100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2409800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2311800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2192100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2158500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2127300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2101200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2120700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2187400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2180100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1230100</v>
+        <v>-2213000</v>
       </c>
       <c r="E100" s="3">
-        <v>3495600</v>
+        <v>1230000</v>
       </c>
       <c r="F100" s="3">
+        <v>3496000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-5406700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4131300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-3137100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2324500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5904900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>142600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-559800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3111000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-166400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3829300</v>
       </c>
-      <c r="P100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2369900</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-296700</v>
+        <v>372000</v>
       </c>
       <c r="E101" s="3">
-        <v>168600</v>
+        <v>-297000</v>
       </c>
       <c r="F101" s="3">
+        <v>169000</v>
+      </c>
+      <c r="G101" s="3">
         <v>-167600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-205700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>216000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-89900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-63600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-20500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-236400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-85600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-341500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21500</v>
       </c>
-      <c r="P101" s="3" t="s">
+      <c r="Q101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-110900</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>449800</v>
+        <v>4000000</v>
       </c>
       <c r="E102" s="3">
-        <v>751600</v>
+        <v>449000</v>
       </c>
       <c r="F102" s="3">
+        <v>752000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1751500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>161400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1319600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5660700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1462000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1954100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>915700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-205200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>41400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-188600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1903700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-70700</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
